--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R338-ModaliteAccueil.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R338-ModaliteAccueil.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -229,7 +229,7 @@
     <t>05</t>
   </si>
   <si>
-    <t>Visite à domicile</t>
+    <t>Visite et soins à domicile</t>
   </si>
   <si>
     <t>06</t>
@@ -364,13 +364,13 @@
     <t>25</t>
   </si>
   <si>
-    <t>Relayage courte durée (quelques heures par jour)</t>
+    <t>Relayage courte durée (&lt; un jour)</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>Relayage longue durée (sur plusieurs jours)</t>
+    <t>Relayage longue durée (&gt; un jour)</t>
   </si>
   <si>
     <t>Soins à domicile</t>
